--- a/Prusa Work/Adhesion Testing/Parameter Sweep Results.xlsx
+++ b/Prusa Work/Adhesion Testing/Parameter Sweep Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github Stuff\Cylindrical-4th-Axis-Printer\Prusa Work\Adhesion Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3AD0FF-1E6E-4749-B3EF-B061117D06CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73D984A-75C5-4C8E-AA14-A6663E879B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{9A173099-7DCB-4C1C-B974-EA2F92F54F4B}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="67">
   <si>
     <t>Run</t>
   </si>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="J8" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K8" t="s">
         <v>11</v>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="J9" s="1">
         <f ca="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="J10" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="N5" s="1" cm="1">
         <f t="array" aca="1" ref="N5:N10" ca="1">_xlfn.SORTBY(_xlfn.SEQUENCE(6),_xlfn.RANDARRAY(6))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" t="s">
         <v>8</v>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O6" t="s">
         <v>9</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="N7" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O7" t="s">
         <v>10</v>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="N8" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="N10" s="1">
         <f ca="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3380,7 +3380,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970423B3-B449-47D8-BD6B-458BD3F2D6C3}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16.7890625" bestFit="1" customWidth="1"/>
@@ -3693,6 +3693,11 @@
         <v>1.75</v>
       </c>
     </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="N2:R2"/>

--- a/Prusa Work/Adhesion Testing/Parameter Sweep Results.xlsx
+++ b/Prusa Work/Adhesion Testing/Parameter Sweep Results.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github Stuff\Cylindrical-4th-Axis-Printer\Prusa Work\Adhesion Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73D984A-75C5-4C8E-AA14-A6663E879B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B761D57-D0D4-4C73-B34F-D64D872C9DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{9A173099-7DCB-4C1C-B974-EA2F92F54F4B}"/>
+    <workbookView xWindow="786" yWindow="738" windowWidth="17280" windowHeight="8910" activeTab="1" xr2:uid="{9A173099-7DCB-4C1C-B974-EA2F92F54F4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial Testing" sheetId="1" r:id="rId1"/>
-    <sheet name="Starting from Printing Settings" sheetId="2" r:id="rId2"/>
+    <sheet name="Final Testing" sheetId="2" r:id="rId2"/>
     <sheet name="Variance Testing" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="68">
   <si>
     <t>Run</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>Printing Temp (C)</t>
+  </si>
+  <si>
+    <t>Making max ironing 2 b/c we don't need to capture the plateau region</t>
   </si>
 </sst>
 </file>
@@ -325,7 +328,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -342,17 +345,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -378,7 +379,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -387,7 +388,7 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -417,8 +418,8 @@
     <sortCondition ref="D4:D64"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{2F1C908E-4ED9-49F6-929F-4A8B13F107AC}" name="Run" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{67FFC248-2D6B-4B39-BB6E-BAA76153EB88}" name="Tested Parameter" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{2F1C908E-4ED9-49F6-929F-4A8B13F107AC}" name="Run" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{67FFC248-2D6B-4B39-BB6E-BAA76153EB88}" name="Tested Parameter" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{948912DA-CFB9-49D0-96D6-83947780F536}" name="Mandrel"/>
     <tableColumn id="4" xr3:uid="{5D4D3EBA-DCC2-4D5D-B940-AF62B010F3DF}" name="Parameter Value"/>
     <tableColumn id="5" xr3:uid="{C47B78D1-1B22-443E-93C6-52F0B8665D5E}" name="Result"/>
@@ -436,14 +437,14 @@
     <sortCondition ref="D4:D28"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{AA07CE71-CEE8-4D2E-A7A6-524809E3D8B0}" name="Run" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{D0BF7365-2B46-4767-AA16-83B9F9B8A557}" name="Tested Parameter" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{AA07CE71-CEE8-4D2E-A7A6-524809E3D8B0}" name="Run" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{D0BF7365-2B46-4767-AA16-83B9F9B8A557}" name="Tested Parameter" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{159046F7-ABED-44C5-853A-72ECA23396EB}" name="Mandrel"/>
     <tableColumn id="8" xr3:uid="{4873FC32-A47C-42E3-A084-6772CB58ACC9}" name="Printing Temp"/>
     <tableColumn id="9" xr3:uid="{268CB309-1E16-4D21-A057-9DF0462257FB}" name="Ironing"/>
-    <tableColumn id="4" xr3:uid="{0EE2B19A-8AAC-4318-BFA9-3EC8A4B71038}" name="Printing Speed" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{AF16D880-582E-4449-81EE-76943D9EBD15}" name="Z Offset" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{4B653234-779B-4988-95F3-7EA19885B045}" name="Flow Multiplier" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{0EE2B19A-8AAC-4318-BFA9-3EC8A4B71038}" name="Printing Speed" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{AF16D880-582E-4449-81EE-76943D9EBD15}" name="Z Offset" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{4B653234-779B-4988-95F3-7EA19885B045}" name="Flow Multiplier" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{A366DFA6-2635-4A9E-9FA1-E351AD74A9AD}" name="Result"/>
     <tableColumn id="6" xr3:uid="{DE7D39B6-D4B2-4DB4-9CB9-05B9B6DBF05C}" name="Notes"/>
     <tableColumn id="7" xr3:uid="{4D304149-9818-4983-82F0-6A71EBE75F2E}" name="Notes For Runs"/>
@@ -456,13 +457,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3387BE5E-C0E7-4C76-9EA0-6E5342B4B4B4}" name="Table4" displayName="Table4" ref="B4:K10" totalsRowShown="0">
   <autoFilter ref="B4:K10" xr:uid="{3387BE5E-C0E7-4C76-9EA0-6E5342B4B4B4}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{39372432-68AB-4CE7-8DB4-E531D3C92CD6}" name="Run" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{39372432-68AB-4CE7-8DB4-E531D3C92CD6}" name="Run" dataDxfId="10"/>
     <tableColumn id="3" xr3:uid="{7E4B1C11-A8F5-41EC-AFC5-F74C85CCD863}" name="Mandrel"/>
     <tableColumn id="4" xr3:uid="{F99BD4E2-9425-4DC4-9581-A56DB577EDD7}" name="Printing Temp (C)"/>
     <tableColumn id="5" xr3:uid="{0148AD17-6D8A-4B14-8C91-A8154EFDEAA2}" name="Ironing"/>
-    <tableColumn id="6" xr3:uid="{7981B0E8-8726-4814-95A5-25C30372FA1D}" name="Printing Speed" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{FE6CBE40-78C3-4E4C-8181-24F4B07B66A1}" name="Z Offset" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{F0581E08-3028-4D27-909F-286AFE01129C}" name="Flow Multiplier" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{7981B0E8-8726-4814-95A5-25C30372FA1D}" name="Printing Speed" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{FE6CBE40-78C3-4E4C-8181-24F4B07B66A1}" name="Z Offset" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{F0581E08-3028-4D27-909F-286AFE01129C}" name="Flow Multiplier" dataDxfId="7"/>
     <tableColumn id="9" xr3:uid="{22D81711-8D6A-40F4-98E9-5F4C7675DDFD}" name="Adhesion Strength (lbs)"/>
     <tableColumn id="10" xr3:uid="{D7F23CBD-5E3A-45EC-9A63-8AE7FACBC828}" name="Notes"/>
     <tableColumn id="11" xr3:uid="{87838DF6-CDCD-4BBD-98A0-92A8829FF2C8}" name="Notes For Runs"/>
@@ -844,13 +845,13 @@
       <c r="J4" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
       <c r="Q4" t="s">
         <v>23</v>
       </c>
@@ -879,7 +880,7 @@
       </c>
       <c r="J5" s="1" cm="1">
         <f t="array" aca="1" ref="J5:J10" ca="1">_xlfn.SORTBY(_xlfn.SEQUENCE(6),_xlfn.RANDARRAY(6))</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L5" t="s">
         <v>8</v>
@@ -918,7 +919,7 @@
       </c>
       <c r="J6" s="1">
         <f ca="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K6" t="s">
         <v>9</v>
@@ -960,7 +961,7 @@
       </c>
       <c r="J7" s="1">
         <f ca="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K7" t="s">
         <v>10</v>
@@ -1002,7 +1003,7 @@
       </c>
       <c r="J8" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K8" t="s">
         <v>11</v>
@@ -1052,7 +1053,7 @@
       </c>
       <c r="J9" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -2251,55 +2252,55 @@
       <c r="A1" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
     </row>
     <row r="2" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
     </row>
     <row r="3" spans="1:21" ht="58.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" t="s">
@@ -2338,13 +2339,13 @@
       <c r="N4" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="P4" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
       <c r="U4" t="s">
         <v>23</v>
       </c>
@@ -2382,7 +2383,7 @@
       </c>
       <c r="N5" s="1" cm="1">
         <f t="array" aca="1" ref="N5:N10" ca="1">_xlfn.SORTBY(_xlfn.SEQUENCE(6),_xlfn.RANDARRAY(6))</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P5" t="s">
         <v>8</v>
@@ -2433,7 +2434,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" t="s">
         <v>9</v>
@@ -2487,7 +2488,7 @@
       </c>
       <c r="N7" s="1">
         <f ca="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O7" t="s">
         <v>10</v>
@@ -2496,7 +2497,7 @@
         <v>280</v>
       </c>
       <c r="Q7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R7" s="6">
         <v>0.7</v>
@@ -2541,7 +2542,7 @@
       </c>
       <c r="N8" s="1">
         <f ca="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -2580,7 +2581,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -2619,7 +2620,7 @@
       </c>
       <c r="N10" s="1">
         <f ca="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -3274,6 +3275,9 @@
       </c>
       <c r="J31" t="s">
         <v>17</v>
+      </c>
+      <c r="L31" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -3400,54 +3404,54 @@
       <c r="A1" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="N2" s="10" t="s">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="N2" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
       <c r="N3" t="s">
         <v>8</v>
       </c>
@@ -3498,19 +3502,19 @@
       <c r="M4" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4">
         <v>240</v>
       </c>
-      <c r="O4" s="12">
-        <v>0</v>
-      </c>
-      <c r="P4" s="13">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="3">
         <v>0.2</v>
       </c>
-      <c r="R4" s="14">
+      <c r="R4" s="10">
         <v>1.5</v>
       </c>
     </row>
@@ -3539,19 +3543,19 @@
       <c r="M5" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="12">
+      <c r="N5">
         <v>280</v>
       </c>
-      <c r="O5" s="12">
-        <v>3</v>
-      </c>
-      <c r="P5" s="13">
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="3">
         <v>0.7</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="3">
         <v>0.3</v>
       </c>
-      <c r="R5" s="14">
+      <c r="R5" s="10">
         <v>2</v>
       </c>
     </row>
@@ -3580,23 +3584,23 @@
       <c r="M6" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="11">
         <f>(N5+N4)/2</f>
         <v>260</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="11">
         <f>_xlfn.FLOOR.MATH((O5+O4)/2)</f>
         <v>1</v>
       </c>
-      <c r="P6" s="15">
+      <c r="P6" s="11">
         <f t="shared" ref="P6:R6" si="0">(P5+P4)/2</f>
         <v>0.44999999999999996</v>
       </c>
-      <c r="Q6" s="15">
+      <c r="Q6" s="11">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="R6" s="16">
+      <c r="R6" s="12">
         <f t="shared" si="0"/>
         <v>1.75</v>
       </c>
